--- a/쿠팡_유아치약_25개_제품목록.xlsx
+++ b/쿠팡_유아치약_25개_제품목록.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,16 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -61,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -70,6 +80,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -635,7 +647,11 @@
           <t>닥터노아 중금속 안심 불소 유아 아기 치약 라즈베리 레몬향, 60g, 1개</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6422565931?itemId=27338652458&amp;vendorItemId=95175834890</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>7080</v>
       </c>
@@ -714,7 +730,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>배지: 구매 1위 / 정가 12,000원 / 할인 41% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>배지: 구매 1위 / 정가 12,000원 / 할인 41% / 주소 확보(딜번호 6422565931)</t>
         </is>
       </c>
     </row>
@@ -749,7 +765,11 @@
           <t>뷰카 주니어 마일드 고불소 구취케어 비건 어린이 치약 포도향, 110g, 4개</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7427543327</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>9800</v>
       </c>
@@ -828,7 +848,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>배지: BEST AWARDS / 정가 20,900원 / 할인 53% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>배지: BEST AWARDS / 정가 20,900원 / 할인 53% / 주소 확보(딜번호 7427543327)</t>
         </is>
       </c>
     </row>
@@ -863,7 +883,11 @@
           <t>닥터노아 중금속 안심 1450 고불소 어린이치약 포도향, 60g, 3개</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9625125018</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>18480</v>
       </c>
@@ -942,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>정가 38,400원 / 할인 51% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 38,400원 / 할인 51% / 주소 확보(딜번호 9625125018)</t>
         </is>
       </c>
     </row>
@@ -977,7 +1001,11 @@
           <t>벨레다 1450 고불소 어린이 치약 스피아민트향, 50g, 1개</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8475675696</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>6500</v>
       </c>
@@ -1056,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>정가 8,500원 / 할인 23% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 8,500원 / 할인 23% / 주소 확보(딜번호 8475675696)</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1119,11 @@
           <t>뷰카 주니어 마일드 고불소 비건치약 110g x 4종 세트 프루티믹스, 110g, 4개입, 1세트</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9427894228</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>12200</v>
       </c>
@@ -1170,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>배지: BEST AWARDS / 정가 20,900원 / 할인 41% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>배지: BEST AWARDS / 정가 20,900원 / 할인 41% / 주소 확보(딜번호 9427894228)</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1237,11 @@
           <t>2080 일사오공 고불소 주니어 치약 애플라임향, 80g, 3개</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7444603797?itemId=19367024138&amp;vendorItemId=86479922183</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>11600</v>
       </c>
@@ -1284,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>정가 21,000원 / 할인 44% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 21,000원 / 할인 44% / 주소 확보(딜번호 7444603797)</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1355,11 @@
           <t>블랑키즐 유아용 고불소 치약 애플망고향, 60g, 1개입, 2개</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7575239396</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>12900</v>
       </c>
@@ -1398,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>정가 24,000원 / 할인 46% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 24,000원 / 할인 46% / 주소 확보(딜번호 7575239396)</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1473,7 @@
           <t>2080 키즈크리닉 4스텝 치약 순한민트향, 80g, 6개</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" t="n">
         <v>9300</v>
       </c>
@@ -1512,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>정가 15,400원 / 할인 39% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>⚠ 주소 확인 필요 — 7444603797 은 06번(2080 일사오공)의 딜번호. 올바른 후보가 기록에 있음: 6456138397 (이름·가격 9,300원 정확히 일치) / 정가 15,400원 / 할인 39% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1587,11 @@
           <t>조르단 뉴스텝1 어린이 불소 치약 딸기향, 90g, 1개</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8428289204</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>4250</v>
       </c>
@@ -1626,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>정가 6,500원 / 할인 34% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 6,500원 / 할인 34% / 주소 확보(딜번호 8428289204)</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1705,7 @@
           <t>티타드 주니어 불소 치약, 60g, 1개</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" t="n">
         <v>7450</v>
       </c>
@@ -1740,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>배지: 브랜드 직매입 / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>⚠ 주소 확인 필요 — 맞춘 것이 60g 1개입 4개 / 28,700원. 찾는 것은 60g 1개 / 7,450원 — 같은 페이지의 다른 옵션일 가능성. 확인 필요 / 배지: 브랜드 직매입 / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1819,11 @@
           <t>에이카랩스 코뿔소 어린이 불소 치약 청포도향, 60g, 1개</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7560673413</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>6400</v>
       </c>
@@ -1854,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>정가 10,000원 / 할인 36% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 10,000원 / 할인 36% / 주소 확보(딜번호 7560673413)</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1937,11 @@
           <t>제니튼 닥터제니 1450 고불소 주니어치약 샤인머스켓향, 60g, 2개</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7923007337</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>14100</v>
       </c>
@@ -1968,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>정가 19,800원 / 할인 28% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 19,800원 / 할인 28% / 주소 확보(딜번호 7923007337)</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2055,11 @@
           <t>조르단 뉴스텝2 어린이 고불소 치약 포도향, 90g, 3개</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8428356943</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>10780</v>
       </c>
@@ -2082,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>정가 19,200원 / 할인 43% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 19,200원 / 할인 43% / 주소 확보(딜번호 8428356943)</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2173,11 @@
           <t>센토 주니어 세이프 고불소 구취케어 비건 어린이치약 풍선껌향, 120g, 1개입, 4개</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9278059411</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>9960</v>
       </c>
@@ -2196,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>정가 21,500원 / 할인 53% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 21,500원 / 할인 53% / 주소 확보(딜번호 9278059411)</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2291,11 @@
           <t>2080 주니어 1450 고불소 충치케어 펌핑치약, 220g, 1개</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8544556420</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>12250</v>
       </c>
@@ -2310,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>정가 23,300원 / 할인 47% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 23,300원 / 할인 47% / 주소 확보(딜번호 8544556420)</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2409,11 @@
           <t>벨레다 어린이 고불소 마일드 민트 치약, 50g, 1개</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9536173729</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>7000</v>
       </c>
@@ -2424,7 +2492,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>주소 확보(딜번호 9536173729)</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2527,11 @@
           <t>오루루 캐치티니핑 고불소치약, 80g, 2개</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9325937896</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>6300</v>
       </c>
@@ -2538,7 +2610,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>주소 확보(딜번호 9325937896)</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2645,11 @@
           <t>조르단 아동용 뉴스텝2 고불소 펌프치약 포도향 188g + 리필 188g 세트, 376g, 1세트</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8599187819</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>17940</v>
       </c>
@@ -2652,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>정가 23,800원 / 할인 24% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 23,800원 / 할인 24% / 주소 확보(딜번호 8599187819)</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2763,11 @@
           <t>뷰카 주니어 마일드 고불소 구취케어 비건 어린이 치약 딸기향, 110g, 4개</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7646155579</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>10990</v>
       </c>
@@ -2766,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>정가 20,900원 / 할인 47% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 20,900원 / 할인 47% / 주소 확보(딜번호 7646155579)</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2881,11 @@
           <t>센토 주니어 세이프 고불소 구취케어 비건 어린이치약 포도향, 120g, 4개</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8803856645</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>9960</v>
       </c>
@@ -2880,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>정가 21,500원 / 할인 53% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 21,500원 / 할인 53% / 주소 확보(딜번호 8803856645)</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2999,11 @@
           <t>라이온 키즈세이프 충치 집중케어 치약, 60g, 3개</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6185905318</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>6340</v>
       </c>
@@ -2994,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>정가 11,250원 / 할인 43% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 11,250원 / 할인 43% / 주소 확보(딜번호 6185905318)</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3117,11 @@
           <t>예꼬맘 3단계 어린이치약 고불소 60g + 미니치약 15g 스피아민트향, 75g, 3세트</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1514135504</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>11700</v>
       </c>
@@ -3108,7 +3200,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>주소 확보(딜번호 1514135504)</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3235,11 @@
           <t>에이카랩스 어린이 코뿔소 치약 사과향 1450ppm, 60g, 2개</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7560527159</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>12800</v>
       </c>
@@ -3222,7 +3318,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>정가 20,000원 / 할인 36% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 20,000원 / 할인 36% / 주소 확보(딜번호 7560527159)</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3353,7 @@
           <t>2080 주니어 자일리 플러스 치약, 80g, 1개입, 6개</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n"/>
+      <c r="G25" s="5" t="n"/>
       <c r="H25" t="n">
         <v>10600</v>
       </c>
@@ -3336,7 +3432,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>정가 20,000원 / 할인 47% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>⚠ 주소 확인 필요 — 7444603797 은 06번(2080 일사오공)의 딜번호. 자일리 플러스는 후보 목록에 아예 없었음 — 다시 찾아야 함 / 정가 20,000원 / 할인 47% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3467,11 @@
           <t>제니튼 닥터제니 저불소 어린이 치약, 60g, 2개</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6326970654</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>8790</v>
       </c>
@@ -3450,7 +3550,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>정가 18,000원 / 할인 51% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>정가 18,000원 / 할인 51% / 주소 확보(딜번호 6326970654)</t>
         </is>
       </c>
     </row>

--- a/쿠팡_유아치약_25개_제품목록.xlsx
+++ b/쿠팡_유아치약_25개_제품목록.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>배지: 구매 1위 / 정가 12,000원 / 할인 41% / 주소 확보(딜번호 6422565931)</t>
+          <t>주소 확보(딜번호 6422565931) / 배지: 구매 1위 / 정가 12,000원 / 할인 41%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>배지: BEST AWARDS / 정가 20,900원 / 할인 53% / 주소 확보(딜번호 7427543327)</t>
+          <t>주소 확보(딜번호 7427543327) / 배지: BEST AWARDS / 정가 20,900원 / 할인 53%</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>정가 38,400원 / 할인 51% / 주소 확보(딜번호 9625125018)</t>
+          <t>주소 확보(딜번호 9625125018) / 정가 38,400원 / 할인 51%</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>정가 8,500원 / 할인 23% / 주소 확보(딜번호 8475675696)</t>
+          <t>주소 확보(딜번호 8475675696) / 정가 8,500원 / 할인 23%</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>배지: BEST AWARDS / 정가 20,900원 / 할인 41% / 주소 확보(딜번호 9427894228)</t>
+          <t>주소 확보(딜번호 9427894228) / 배지: BEST AWARDS / 정가 20,900원 / 할인 41%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>정가 21,000원 / 할인 44% / 주소 확보(딜번호 7444603797)</t>
+          <t>주소 확보(딜번호 7444603797) / 정가 21,000원 / 할인 44%</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>정가 24,000원 / 할인 46% / 주소 확보(딜번호 7575239396)</t>
+          <t>주소 확보(딜번호 7575239396) / 정가 24,000원 / 할인 46%</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,11 @@
           <t>2080 키즈크리닉 4스텝 치약 순한민트향, 80g, 6개</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6456138397?itemId=19679031966&amp;vendorItemId=70185039822</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>9300</v>
       </c>
@@ -1552,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>⚠ 주소 확인 필요 — 7444603797 은 06번(2080 일사오공)의 딜번호. 올바른 후보가 기록에 있음: 6456138397 (이름·가격 9,300원 정확히 일치) / 정가 15,400원 / 할인 39% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>주소 확보(딜번호 6456138397) / 정가 15,400원 / 할인 39%</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>정가 6,500원 / 할인 34% / 주소 확보(딜번호 8428289204)</t>
+          <t>주소 확보(딜번호 8428289204) / 정가 6,500원 / 할인 34%</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1709,11 @@
           <t>티타드 주니어 불소 치약, 60g, 1개</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9167355510</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>7450</v>
       </c>
@@ -1784,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>⚠ 주소 확인 필요 — 맞춘 것이 60g 1개입 4개 / 28,700원. 찾는 것은 60g 1개 / 7,450원 — 같은 페이지의 다른 옵션일 가능성. 확인 필요 / 배지: 브랜드 직매입 / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>주소 확보(딜번호 9167355510) / 맞춘 것이 60g 1개입 4개 / 28,700원. 찾는 것은 60g 1개 / 배지: 브랜드 직매입 / 주소는 옵션 선택형 페이지라 기본값이 60g 4개입(28,700원)으로 열림. 같은 상품 페이지의 다른 옵션이므로 상세페이지(USP) 수집에는 지장 없음. 표의 판매가·용량은 순위 캡쳐 실측값(60g 1개 / 7,450원)으로 그대로 둠.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>정가 10,000원 / 할인 36% / 주소 확보(딜번호 7560673413)</t>
+          <t>주소 확보(딜번호 7560673413) / 정가 10,000원 / 할인 36%</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>정가 19,800원 / 할인 28% / 주소 확보(딜번호 7923007337)</t>
+          <t>주소 확보(딜번호 7923007337) / 정가 19,800원 / 할인 28%</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>정가 19,200원 / 할인 43% / 주소 확보(딜번호 8428356943)</t>
+          <t>주소 확보(딜번호 8428356943) / 정가 19,200원 / 할인 43%</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2264,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>정가 21,500원 / 할인 53% / 주소 확보(딜번호 9278059411)</t>
+          <t>주소 확보(딜번호 9278059411) / 정가 21,500원 / 할인 53%</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2301,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8544556420</t>
+          <t>https://www.coupang.com/vp/products/8544556420?itemId=24739992049&amp;vendorItemId=91748701080</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2374,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>정가 23,300원 / 할인 47% / 주소 확보(딜번호 8544556420)</t>
+          <t>주소 확보(딜번호 8544556420) / 정가 23,300원 / 할인 47%</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2736,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>정가 23,800원 / 할인 24% / 주소 확보(딜번호 8599187819)</t>
+          <t>주소 확보(딜번호 8599187819) / 정가 23,800원 / 할인 24%</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2854,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>정가 20,900원 / 할인 47% / 주소 확보(딜번호 7646155579)</t>
+          <t>주소 확보(딜번호 7646155579) / 정가 20,900원 / 할인 47%</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>정가 21,500원 / 할인 53% / 주소 확보(딜번호 8803856645)</t>
+          <t>주소 확보(딜번호 8803856645) / 정가 21,500원 / 할인 53%</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3090,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>정가 11,250원 / 할인 43% / 주소 확보(딜번호 6185905318)</t>
+          <t>주소 확보(딜번호 6185905318) / 정가 11,250원 / 할인 43%</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3326,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>정가 20,000원 / 할인 36% / 주소 확보(딜번호 7560527159)</t>
+          <t>주소 확보(딜번호 7560527159) / 정가 20,000원 / 할인 36%</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3361,11 @@
           <t>2080 주니어 자일리 플러스 치약, 80g, 1개입, 6개</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7370916424?itemId=19013436188&amp;vendorItemId=74160017357</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>10600</v>
       </c>
@@ -3432,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>⚠ 주소 확인 필요 — 7444603797 은 06번(2080 일사오공)의 딜번호. 자일리 플러스는 후보 목록에 아예 없었음 — 다시 찾아야 함 / 정가 20,000원 / 할인 47% / 쿠팡URL 미확보 — 캡쳐가 모바일 앱 화면이라 주소 미노출. 확장프로그램 검색 단계에서 채울 것</t>
+          <t>주소 확보(딜번호 7370916424) / 정가 20,000원 / 할인 47%</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3562,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>정가 18,000원 / 할인 51% / 주소 확보(딜번호 6326970654)</t>
+          <t>주소 확보(딜번호 6326970654) / 정가 18,000원 / 할인 51%</t>
         </is>
       </c>
     </row>

--- a/쿠팡_유아치약_25개_제품목록.xlsx
+++ b/쿠팡_유아치약_25개_제품목록.xlsx
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>주소 확보(딜번호 9167355510) / 맞춘 것이 60g 1개입 4개 / 28,700원. 찾는 것은 60g 1개 / 배지: 브랜드 직매입 / 주소는 옵션 선택형 페이지라 기본값이 60g 4개입(28,700원)으로 열림. 같은 상품 페이지의 다른 옵션이므로 상세페이지(USP) 수집에는 지장 없음. 표의 판매가·용량은 순위 캡쳐 실측값(60g 1개 / 7,450원)으로 그대로 둠.</t>
+          <t>주소 확보(딜번호 9167355510) / 배지: 브랜드 직매입 / 주소는 옵션 선택형 페이지라 기본값이 60g 4개입(28,700원)으로 열림. 같은 상품 페이지의 다른 옵션이므로 상세페이지(USP) 수집에는 지장 없음. 표의 판매가·용량은 순위 캡쳐 실측값(60g 1개 / 7,450원)</t>
         </is>
       </c>
     </row>
